--- a/SCRIBE_config_etablissement.xlsx
+++ b/SCRIBE_config_etablissement.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Centre Hospitalier de Valmont</t>
+          <t>Centre Hospitalier — À renseigner</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>CHV</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>1 avenue de l'Hôpital, 74000 Valmont</t>
+          <t>1 avenue de l'Hôpital, 74000 votre ville</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>12 rue des Soins, 74100 Crestval</t>
+          <t>12 rue des Soins, 74100 ville 2</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>5 chemin du Lac, 74200 Les Pins</t>
+          <t>5 chemin du Lac, 74200 site 3</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>1 avenue de l'Hôpital, 74000 Valmont</t>
+          <t>1 avenue de l'Hôpital, 74000 votre ville</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>04 50 00 00 15</t>
+          <t>0X 50 00 00 15</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>04 50 00 00 18</t>
+          <t>0X 50 00 00 18</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr"/>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>04 50 00 01 00</t>
+          <t>0X 50 00 01 00</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>04 50 00 02 00</t>
+          <t>0X 50 00 02 00</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>04 50 00 00 50</t>
+          <t>0X 50 00 00 50</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>04 50 00 03 00</t>
+          <t>0X 50 00 03 00</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>04 50 00 04 00</t>
+          <t>0X 50 00 04 00</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr"/>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>04 50 00 05 00</t>
+          <t>0X 50 00 05 00</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>04 50 00 06 00</t>
+          <t>0X 50 00 06 00</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>04 50 00 07 00</t>
+          <t>0X 50 00 07 00</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>04 50 00 08 00</t>
+          <t>0X 50 00 08 00</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>04 50 00 09 00</t>
+          <t>0X 50 00 09 00</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>04 50 00 10 00</t>
+          <t>0X 50 00 10 00</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>04 50 00 40 00</t>
+          <t>0X 50 00 40 00</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>04 50 00 00 99</t>
+          <t>0X 50 00 00 99</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>04 50 00 00 00</t>
+          <t>0X 50 00 00 00</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -2098,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2158,682 +2158,578 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t>Cardiologie USC</t>
+          <t>Urgences Adultes</t>
         </is>
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>URGENCES</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr"/>
       <c r="E4" s="24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F4" s="24" t="inlineStr"/>
+      <c r="F4" s="24" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Cardiologie</t>
+          <t>Uhcd</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>URGENCES</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr"/>
       <c r="E5" s="24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr"/>
+      <c r="F5" s="24" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>Dermatologie</t>
+          <t>Smur</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>URGENCES</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr"/>
       <c r="E6" s="24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F6" s="24" t="inlineStr"/>
+      <c r="F6" s="24" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>HDJ Médecine</t>
+          <t>Urgences Pediatriques</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>URGENCES</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr"/>
       <c r="E7" s="24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F7" s="24" t="inlineStr"/>
+      <c r="F7" s="24" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>Hématologie</t>
+          <t>Reanimation Adultes</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>SOINS CRITIQUES</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr"/>
       <c r="E8" s="24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr"/>
+      <c r="F8" s="24" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Hépato-Gastroentérologie</t>
+          <t>Soins Continus</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>SOINS CRITIQUES</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr"/>
       <c r="E9" s="24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr"/>
+      <c r="F9" s="24" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>Infectiologie HC</t>
+          <t>Usic</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>SOINS CRITIQUES</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr"/>
       <c r="E10" s="24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F10" s="24" t="inlineStr"/>
+      <c r="F10" s="24" t="n"/>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Néphrologie</t>
+          <t>Bloc Operatoire Central</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>CHIRURGIE</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr"/>
       <c r="E11" s="24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F11" s="24" t="inlineStr"/>
+      <c r="F11" s="24" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>Neurologie</t>
+          <t>Chirurgie Viscerale</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>CHIRURGIE</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr"/>
       <c r="E12" s="24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F12" s="24" t="inlineStr"/>
+      <c r="F12" s="24" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Neurologie Post-Aigu UNV</t>
+          <t>Chirurgie Orthopedique</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>CHIRURGIE</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr"/>
       <c r="E13" s="24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F13" s="24" t="inlineStr"/>
+      <c r="F13" s="24" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>Neurologie SI UNV</t>
+          <t>Chirurgie Ambulatoire</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>CHIRURGIE</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr"/>
       <c r="E14" s="24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F14" s="24" t="inlineStr"/>
+      <c r="F14" s="24" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Oncologie</t>
+          <t>Medecine Interne</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>MEDECINE</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr"/>
       <c r="E15" s="24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F15" s="24" t="inlineStr"/>
+      <c r="F15" s="24" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>Pneumologie</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>MEDECINE</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr"/>
       <c r="E16" s="24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F16" s="24" t="inlineStr"/>
+      <c r="F16" s="24" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>Rhumatologie</t>
+          <t>Pneumologie</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>MEDECINE</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr"/>
       <c r="E17" s="24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F17" s="24" t="inlineStr"/>
+      <c r="F17" s="24" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>Gériatrie Aiguë</t>
+          <t>Neurologie</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>MEDECINE</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr"/>
       <c r="E18" s="24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F18" s="24" t="inlineStr"/>
+      <c r="F18" s="24" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>UPUM</t>
+          <t>Gastro-Enterologie</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>MEDECINE</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr"/>
       <c r="E19" s="24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F19" s="24" t="inlineStr">
-        <is>
-          <t>Unité Post-Urgences</t>
-        </is>
-      </c>
+      <c r="F19" s="24" t="n"/>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>Unité Hivernale</t>
+          <t>Infectiologie</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>MEDECINE</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr"/>
       <c r="E20" s="24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F20" s="24" t="inlineStr"/>
+      <c r="F20" s="24" t="n"/>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>Unité Hivernale 2</t>
+          <t>Nephrologie / Hemodialyse</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>MEDECINE</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr"/>
       <c r="E21" s="24" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F21" s="24" t="inlineStr"/>
+      <c r="F21" s="24" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>Chirurgie Cardiaque</t>
+          <t>Maternite / Gynecologie</t>
         </is>
       </c>
       <c r="C22" s="25" t="inlineStr">
         <is>
-          <t>CHIRURGIE ANESTHESIE</t>
-        </is>
-      </c>
-      <c r="D22" s="25" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>MATERNITE PEDIATRIE</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr"/>
       <c r="E22" s="25" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F22" s="25" t="inlineStr"/>
+      <c r="F22" s="25" t="n"/>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="25" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>Chirurgie Digestive</t>
+          <t>Bloc Accouchement</t>
         </is>
       </c>
       <c r="C23" s="25" t="inlineStr">
         <is>
-          <t>CHIRURGIE ANESTHESIE</t>
-        </is>
-      </c>
-      <c r="D23" s="25" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>MATERNITE PEDIATRIE</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr"/>
       <c r="E23" s="25" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F23" s="25" t="inlineStr"/>
+      <c r="F23" s="25" t="n"/>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>Gynécologie Chirurgicale</t>
+          <t>Neonatologie</t>
         </is>
       </c>
       <c r="C24" s="25" t="inlineStr">
         <is>
-          <t>CHIRURGIE ANESTHESIE</t>
-        </is>
-      </c>
-      <c r="D24" s="25" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>MATERNITE PEDIATRIE</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="inlineStr"/>
       <c r="E24" s="25" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F24" s="25" t="inlineStr">
-        <is>
-          <t>Femmes uniquement</t>
-        </is>
-      </c>
+      <c r="F24" s="25" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>Neurochirurgie</t>
+          <t>Pediatrie Generale</t>
         </is>
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
-          <t>CHIRURGIE ANESTHESIE</t>
-        </is>
-      </c>
-      <c r="D25" s="25" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>MATERNITE PEDIATRIE</t>
+        </is>
+      </c>
+      <c r="D25" s="25" t="inlineStr"/>
       <c r="E25" s="25" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F25" s="25" t="inlineStr"/>
+      <c r="F25" s="25" t="n"/>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>Orthopédie Traumatologie</t>
+          <t>Court Sejour Geriatrique</t>
         </is>
       </c>
       <c r="C26" s="25" t="inlineStr">
         <is>
-          <t>CHIRURGIE ANESTHESIE</t>
-        </is>
-      </c>
-      <c r="D26" s="25" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>GERIATRIE</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr"/>
       <c r="E26" s="25" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F26" s="25" t="inlineStr"/>
+      <c r="F26" s="25" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="25" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>ORL / Ophtalmologie / CMF</t>
+          <t>Ssr Geriatrique</t>
         </is>
       </c>
       <c r="C27" s="25" t="inlineStr">
         <is>
-          <t>CHIRURGIE ANESTHESIE</t>
-        </is>
-      </c>
-      <c r="D27" s="25" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>GERIATRIE</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr"/>
       <c r="E27" s="25" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F27" s="25" t="inlineStr"/>
+      <c r="F27" s="25" t="n"/>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="25" t="inlineStr">
@@ -2843,854 +2739,466 @@
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>Urologie / Thoracique / Vasc.</t>
+          <t>Ehpad</t>
         </is>
       </c>
       <c r="C28" s="25" t="inlineStr">
         <is>
-          <t>CHIRURGIE ANESTHESIE</t>
-        </is>
-      </c>
-      <c r="D28" s="25" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>GERIATRIE</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr"/>
       <c r="E28" s="25" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F28" s="25" t="inlineStr"/>
+      <c r="F28" s="25" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="25" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>Anesthésiologie SSPI</t>
+          <t>Radiologie / Scanner</t>
         </is>
       </c>
       <c r="C29" s="25" t="inlineStr">
         <is>
-          <t>CHIRURGIE ANESTHESIE</t>
-        </is>
-      </c>
-      <c r="D29" s="25" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>IMAGERIE BIOLOGIE</t>
+        </is>
+      </c>
+      <c r="D29" s="25" t="inlineStr"/>
       <c r="E29" s="25" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F29" s="25" t="inlineStr"/>
+      <c r="F29" s="25" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="26" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="B30" s="26" t="inlineStr">
         <is>
-          <t>Réanimation Polyvalente</t>
+          <t>Irm</t>
         </is>
       </c>
       <c r="C30" s="26" t="inlineStr">
         <is>
-          <t>SOINS CRITIQUES</t>
-        </is>
-      </c>
-      <c r="D30" s="26" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>IMAGERIE BIOLOGIE</t>
+        </is>
+      </c>
+      <c r="D30" s="26" t="inlineStr"/>
       <c r="E30" s="26" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F30" s="26" t="inlineStr"/>
+      <c r="F30" s="26" t="n"/>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="26" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="B31" s="26" t="inlineStr">
         <is>
-          <t>SIPO</t>
+          <t>Laboratoire Biochimie</t>
         </is>
       </c>
       <c r="C31" s="26" t="inlineStr">
         <is>
-          <t>SOINS CRITIQUES</t>
-        </is>
-      </c>
-      <c r="D31" s="26" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>IMAGERIE BIOLOGIE</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="inlineStr"/>
       <c r="E31" s="26" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F31" s="26" t="inlineStr">
-        <is>
-          <t>Soins Intensifs Post-Op</t>
-        </is>
-      </c>
+      <c r="F31" s="26" t="n"/>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>UHCD</t>
+          <t>Laboratoire Microbiologie</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>URGENCES</t>
-        </is>
-      </c>
-      <c r="D32" s="20" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>IMAGERIE BIOLOGIE</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr"/>
       <c r="E32" s="20" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F32" s="20" t="inlineStr"/>
+      <c r="F32" s="20" t="n"/>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="B33" s="26" t="inlineStr">
         <is>
-          <t>USIP</t>
+          <t>Pharmacie</t>
         </is>
       </c>
       <c r="C33" s="26" t="inlineStr">
         <is>
-          <t>SOINS CRITIQUES</t>
-        </is>
-      </c>
-      <c r="D33" s="26" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>PHARMACIE</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="inlineStr"/>
       <c r="E33" s="26" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F33" s="26" t="inlineStr"/>
+      <c r="F33" s="26" t="n"/>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="27" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>8002</t>
         </is>
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>USIC</t>
+          <t>Sterilisation Centrale</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
         <is>
-          <t>CARDIOVASCULAIRE</t>
-        </is>
-      </c>
-      <c r="D34" s="27" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>PHARMACIE</t>
+        </is>
+      </c>
+      <c r="D34" s="27" t="inlineStr"/>
       <c r="E34" s="27" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F34" s="27" t="inlineStr"/>
+      <c r="F34" s="27" t="n"/>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="28" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="B35" s="28" t="inlineStr">
         <is>
-          <t>Soins Palliatifs</t>
+          <t>Medecine Polyvalente</t>
         </is>
       </c>
       <c r="C35" s="28" t="inlineStr">
         <is>
-          <t>GERIATRIE</t>
-        </is>
-      </c>
-      <c r="D35" s="28" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>MEDECINE</t>
+        </is>
+      </c>
+      <c r="D35" s="28" t="inlineStr"/>
       <c r="E35" s="28" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F35" s="28" t="inlineStr"/>
+      <c r="F35" s="28" t="n"/>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="29" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="B36" s="29" t="inlineStr">
         <is>
-          <t>Grands Enfants</t>
+          <t>Bloc Operatoire Secondaire</t>
         </is>
       </c>
       <c r="C36" s="29" t="inlineStr">
         <is>
-          <t>FME</t>
-        </is>
-      </c>
-      <c r="D36" s="29" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>CHIRURGIE</t>
+        </is>
+      </c>
+      <c r="D36" s="29" t="inlineStr"/>
       <c r="E36" s="29" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F36" s="29" t="inlineStr"/>
+      <c r="F36" s="29" t="n"/>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="29" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>9003</t>
         </is>
       </c>
       <c r="B37" s="29" t="inlineStr">
         <is>
-          <t>Néonatologie</t>
+          <t>Urgences Site Secondaire</t>
         </is>
       </c>
       <c r="C37" s="29" t="inlineStr">
         <is>
-          <t>FME</t>
-        </is>
-      </c>
-      <c r="D37" s="29" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>URGENCES</t>
+        </is>
+      </c>
+      <c r="D37" s="29" t="inlineStr"/>
       <c r="E37" s="29" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F37" s="29" t="inlineStr"/>
+      <c r="F37" s="29" t="n"/>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="29" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="B38" s="29" t="inlineStr">
         <is>
-          <t>Nourrissons</t>
+          <t>Direction Generale</t>
         </is>
       </c>
       <c r="C38" s="29" t="inlineStr">
         <is>
-          <t>FME</t>
-        </is>
-      </c>
-      <c r="D38" s="29" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>DIRECTION SUPPORT</t>
+        </is>
+      </c>
+      <c r="D38" s="29" t="inlineStr"/>
       <c r="E38" s="29" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F38" s="29" t="inlineStr"/>
+      <c r="F38" s="29" t="n"/>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="29" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="B39" s="29" t="inlineStr">
         <is>
-          <t>Obstétrique</t>
+          <t>Dsi Informatique</t>
         </is>
       </c>
       <c r="C39" s="29" t="inlineStr">
         <is>
-          <t>FME</t>
-        </is>
-      </c>
-      <c r="D39" s="29" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>DIRECTION SUPPORT</t>
+        </is>
+      </c>
+      <c r="D39" s="29" t="inlineStr"/>
       <c r="E39" s="29" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F39" s="29" t="inlineStr">
-        <is>
-          <t>Femmes uniquement</t>
-        </is>
-      </c>
+      <c r="F39" s="29" t="n"/>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="29" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="B40" s="29" t="inlineStr">
         <is>
-          <t>USIP Pédiatrie</t>
+          <t>Services Techniques</t>
         </is>
       </c>
       <c r="C40" s="29" t="inlineStr">
         <is>
-          <t>FME</t>
-        </is>
-      </c>
-      <c r="D40" s="29" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
+          <t>DIRECTION SUPPORT</t>
+        </is>
+      </c>
+      <c r="D40" s="29" t="inlineStr"/>
       <c r="E40" s="29" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="F40" s="29" t="inlineStr"/>
+      <c r="F40" s="29" t="n"/>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="30" t="inlineStr">
-        <is>
-          <t>8003</t>
-        </is>
-      </c>
-      <c r="B41" s="30" t="inlineStr">
-        <is>
-          <t>Unité Psychiatrie A</t>
-        </is>
-      </c>
-      <c r="C41" s="30" t="inlineStr">
-        <is>
-          <t>SANTE MENTALE</t>
-        </is>
-      </c>
-      <c r="D41" s="30" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
-      <c r="E41" s="30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F41" s="30" t="inlineStr"/>
+      <c r="A41" s="30" t="n"/>
+      <c r="B41" s="30" t="n"/>
+      <c r="C41" s="30" t="n"/>
+      <c r="D41" s="30" t="n"/>
+      <c r="E41" s="30" t="n"/>
+      <c r="F41" s="30" t="n"/>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="30" t="inlineStr">
-        <is>
-          <t>8200</t>
-        </is>
-      </c>
-      <c r="B42" s="30" t="inlineStr">
-        <is>
-          <t>UPUP Adultes</t>
-        </is>
-      </c>
-      <c r="C42" s="30" t="inlineStr">
-        <is>
-          <t>SANTE MENTALE</t>
-        </is>
-      </c>
-      <c r="D42" s="30" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
-      <c r="E42" s="30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F42" s="30" t="inlineStr"/>
+      <c r="A42" s="30" t="n"/>
+      <c r="B42" s="30" t="n"/>
+      <c r="C42" s="30" t="n"/>
+      <c r="D42" s="30" t="n"/>
+      <c r="E42" s="30" t="n"/>
+      <c r="F42" s="30" t="n"/>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="30" t="inlineStr">
-        <is>
-          <t>8250</t>
-        </is>
-      </c>
-      <c r="B43" s="30" t="inlineStr">
-        <is>
-          <t>UPUP Adolescents</t>
-        </is>
-      </c>
-      <c r="C43" s="30" t="inlineStr">
-        <is>
-          <t>SANTE MENTALE</t>
-        </is>
-      </c>
-      <c r="D43" s="30" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
-      <c r="E43" s="30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F43" s="30" t="inlineStr"/>
+      <c r="A43" s="30" t="n"/>
+      <c r="B43" s="30" t="n"/>
+      <c r="C43" s="30" t="n"/>
+      <c r="D43" s="30" t="n"/>
+      <c r="E43" s="30" t="n"/>
+      <c r="F43" s="30" t="n"/>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="30" t="inlineStr">
-        <is>
-          <t>5020</t>
-        </is>
-      </c>
-      <c r="B44" s="30" t="inlineStr">
-        <is>
-          <t>Addictologie</t>
-        </is>
-      </c>
-      <c r="C44" s="30" t="inlineStr">
-        <is>
-          <t>SANTE MENTALE</t>
-        </is>
-      </c>
-      <c r="D44" s="30" t="inlineStr">
-        <is>
-          <t>Site Secondaire</t>
-        </is>
-      </c>
-      <c r="E44" s="30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F44" s="30" t="inlineStr"/>
+      <c r="A44" s="30" t="n"/>
+      <c r="B44" s="30" t="n"/>
+      <c r="C44" s="30" t="n"/>
+      <c r="D44" s="30" t="n"/>
+      <c r="E44" s="30" t="n"/>
+      <c r="F44" s="30" t="n"/>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="27" t="inlineStr">
-        <is>
-          <t>5620</t>
-        </is>
-      </c>
-      <c r="B45" s="27" t="inlineStr">
-        <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="C45" s="27" t="inlineStr">
-        <is>
-          <t>CARDIOVASCULAIRE</t>
-        </is>
-      </c>
-      <c r="D45" s="27" t="inlineStr">
-        <is>
-          <t>Site Secondaire</t>
-        </is>
-      </c>
-      <c r="E45" s="27" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F45" s="27" t="inlineStr"/>
+      <c r="A45" s="27" t="n"/>
+      <c r="B45" s="27" t="n"/>
+      <c r="C45" s="27" t="n"/>
+      <c r="D45" s="27" t="n"/>
+      <c r="E45" s="27" t="n"/>
+      <c r="F45" s="27" t="n"/>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>7320</t>
-        </is>
-      </c>
-      <c r="B46" s="25" t="inlineStr">
-        <is>
-          <t>Chirurgie</t>
-        </is>
-      </c>
-      <c r="C46" s="25" t="inlineStr">
-        <is>
-          <t>CHIRURGIE ANESTHESIE</t>
-        </is>
-      </c>
-      <c r="D46" s="25" t="inlineStr">
-        <is>
-          <t>Site Secondaire</t>
-        </is>
-      </c>
-      <c r="E46" s="25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F46" s="25" t="inlineStr"/>
+      <c r="A46" s="25" t="n"/>
+      <c r="B46" s="25" t="n"/>
+      <c r="C46" s="25" t="n"/>
+      <c r="D46" s="25" t="n"/>
+      <c r="E46" s="25" t="n"/>
+      <c r="F46" s="25" t="n"/>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="24" t="inlineStr">
-        <is>
-          <t>5430</t>
-        </is>
-      </c>
-      <c r="B47" s="24" t="inlineStr">
-        <is>
-          <t>Médecine Polyvalente</t>
-        </is>
-      </c>
-      <c r="C47" s="24" t="inlineStr">
-        <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D47" s="24" t="inlineStr">
-        <is>
-          <t>Site Secondaire</t>
-        </is>
-      </c>
-      <c r="E47" s="24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F47" s="24" t="inlineStr"/>
+      <c r="A47" s="24" t="n"/>
+      <c r="B47" s="24" t="n"/>
+      <c r="C47" s="24" t="n"/>
+      <c r="D47" s="24" t="n"/>
+      <c r="E47" s="24" t="n"/>
+      <c r="F47" s="24" t="n"/>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="24" t="inlineStr">
-        <is>
-          <t>5970</t>
-        </is>
-      </c>
-      <c r="B48" s="24" t="inlineStr">
-        <is>
-          <t>Neurologie UNV</t>
-        </is>
-      </c>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="inlineStr">
-        <is>
-          <t>Site Secondaire</t>
-        </is>
-      </c>
-      <c r="E48" s="24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F48" s="24" t="inlineStr"/>
+      <c r="A48" s="24" t="n"/>
+      <c r="B48" s="24" t="n"/>
+      <c r="C48" s="24" t="n"/>
+      <c r="D48" s="24" t="n"/>
+      <c r="E48" s="24" t="n"/>
+      <c r="F48" s="24" t="n"/>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="29" t="inlineStr">
-        <is>
-          <t>7740</t>
-        </is>
-      </c>
-      <c r="B49" s="29" t="inlineStr">
-        <is>
-          <t>Obstétrique</t>
-        </is>
-      </c>
-      <c r="C49" s="29" t="inlineStr">
-        <is>
-          <t>FME</t>
-        </is>
-      </c>
-      <c r="D49" s="29" t="inlineStr">
-        <is>
-          <t>Site Secondaire</t>
-        </is>
-      </c>
-      <c r="E49" s="29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F49" s="29" t="inlineStr">
-        <is>
-          <t>Femmes uniquement</t>
-        </is>
-      </c>
+      <c r="A49" s="29" t="n"/>
+      <c r="B49" s="29" t="n"/>
+      <c r="C49" s="29" t="n"/>
+      <c r="D49" s="29" t="n"/>
+      <c r="E49" s="29" t="n"/>
+      <c r="F49" s="29" t="n"/>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="24" t="inlineStr">
-        <is>
-          <t>6140</t>
-        </is>
-      </c>
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>Pneumologie</t>
-        </is>
-      </c>
-      <c r="C50" s="24" t="inlineStr">
-        <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D50" s="24" t="inlineStr">
-        <is>
-          <t>Site Secondaire</t>
-        </is>
-      </c>
-      <c r="E50" s="24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F50" s="24" t="inlineStr"/>
+      <c r="A50" s="24" t="n"/>
+      <c r="B50" s="24" t="n"/>
+      <c r="C50" s="24" t="n"/>
+      <c r="D50" s="24" t="n"/>
+      <c r="E50" s="24" t="n"/>
+      <c r="F50" s="24" t="n"/>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="26" t="inlineStr">
-        <is>
-          <t>7920</t>
-        </is>
-      </c>
-      <c r="B51" s="26" t="inlineStr">
-        <is>
-          <t>Soins Continus</t>
-        </is>
-      </c>
-      <c r="C51" s="26" t="inlineStr">
-        <is>
-          <t>SOINS CRITIQUES</t>
-        </is>
-      </c>
-      <c r="D51" s="26" t="inlineStr">
-        <is>
-          <t>Site Secondaire</t>
-        </is>
-      </c>
-      <c r="E51" s="26" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F51" s="26" t="inlineStr"/>
+      <c r="A51" s="26" t="n"/>
+      <c r="B51" s="26" t="n"/>
+      <c r="C51" s="26" t="n"/>
+      <c r="D51" s="26" t="n"/>
+      <c r="E51" s="26" t="n"/>
+      <c r="F51" s="26" t="n"/>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="28" t="inlineStr">
-        <is>
-          <t>5550</t>
-        </is>
-      </c>
-      <c r="B52" s="28" t="inlineStr">
-        <is>
-          <t>Gériatrie Aiguë</t>
-        </is>
-      </c>
-      <c r="C52" s="28" t="inlineStr">
-        <is>
-          <t>GERIATRIE</t>
-        </is>
-      </c>
-      <c r="D52" s="28" t="inlineStr">
-        <is>
-          <t>Site Secondaire</t>
-        </is>
-      </c>
-      <c r="E52" s="28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F52" s="28" t="inlineStr"/>
+      <c r="A52" s="28" t="n"/>
+      <c r="B52" s="28" t="n"/>
+      <c r="C52" s="28" t="n"/>
+      <c r="D52" s="28" t="n"/>
+      <c r="E52" s="28" t="n"/>
+      <c r="F52" s="28" t="n"/>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="31" t="inlineStr">
-        <is>
-          <t>DSI</t>
-        </is>
-      </c>
-      <c r="B53" s="31" t="inlineStr">
-        <is>
-          <t>Informatique / DSI</t>
-        </is>
-      </c>
-      <c r="C53" s="31" t="inlineStr">
-        <is>
-          <t>SUPPORT</t>
-        </is>
-      </c>
-      <c r="D53" s="31" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
-      <c r="E53" s="31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F53" s="31" t="inlineStr">
-        <is>
-          <t>Incidents cyber</t>
-        </is>
-      </c>
+      <c r="A53" s="31" t="n"/>
+      <c r="B53" s="31" t="n"/>
+      <c r="C53" s="31" t="n"/>
+      <c r="D53" s="31" t="n"/>
+      <c r="E53" s="31" t="n"/>
+      <c r="F53" s="31" t="n"/>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="31" t="inlineStr">
-        <is>
-          <t>LOG</t>
-        </is>
-      </c>
-      <c r="B54" s="31" t="inlineStr">
-        <is>
-          <t>Logistique</t>
-        </is>
-      </c>
-      <c r="C54" s="31" t="inlineStr">
-        <is>
-          <t>SUPPORT</t>
-        </is>
-      </c>
-      <c r="D54" s="31" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
-      <c r="E54" s="31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F54" s="31" t="inlineStr"/>
+      <c r="A54" s="31" t="n"/>
+      <c r="B54" s="31" t="n"/>
+      <c r="C54" s="31" t="n"/>
+      <c r="D54" s="31" t="n"/>
+      <c r="E54" s="31" t="n"/>
+      <c r="F54" s="31" t="n"/>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="32" t="inlineStr">
-        <is>
-          <t>PHA</t>
-        </is>
-      </c>
-      <c r="B55" s="32" t="inlineStr">
-        <is>
-          <t>Pharmacie</t>
-        </is>
-      </c>
-      <c r="C55" s="32" t="inlineStr">
-        <is>
-          <t>MEDICO-TECHNIQUE ET REEDUCATION</t>
-        </is>
-      </c>
-      <c r="D55" s="32" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
-      <c r="E55" s="32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F55" s="32" t="inlineStr"/>
+      <c r="A55" s="32" t="n"/>
+      <c r="B55" s="32" t="n"/>
+      <c r="C55" s="32" t="n"/>
+      <c r="D55" s="32" t="n"/>
+      <c r="E55" s="32" t="n"/>
+      <c r="F55" s="32" t="n"/>
     </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="32" t="inlineStr">
-        <is>
-          <t>LAB</t>
-        </is>
-      </c>
-      <c r="B56" s="32" t="inlineStr">
-        <is>
-          <t>Laboratoire</t>
-        </is>
-      </c>
-      <c r="C56" s="32" t="inlineStr">
-        <is>
-          <t>MEDICO-TECHNIQUE ET REEDUCATION</t>
-        </is>
-      </c>
-      <c r="D56" s="32" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
-      <c r="E56" s="32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F56" s="32" t="inlineStr"/>
+      <c r="A56" s="32" t="n"/>
+      <c r="B56" s="32" t="n"/>
+      <c r="C56" s="32" t="n"/>
+      <c r="D56" s="32" t="n"/>
+      <c r="E56" s="32" t="n"/>
+      <c r="F56" s="32" t="n"/>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="32" t="inlineStr">
-        <is>
-          <t>IMG</t>
-        </is>
-      </c>
-      <c r="B57" s="32" t="inlineStr">
-        <is>
-          <t>Imagerie / Radiologie</t>
-        </is>
-      </c>
-      <c r="C57" s="32" t="inlineStr">
-        <is>
-          <t>MEDICO-TECHNIQUE ET REEDUCATION</t>
-        </is>
-      </c>
-      <c r="D57" s="32" t="inlineStr">
-        <is>
-          <t>Site Principal</t>
-        </is>
-      </c>
-      <c r="E57" s="32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F57" s="32" t="inlineStr"/>
-    </row>
+      <c r="A57" s="32" t="n"/>
+      <c r="B57" s="32" t="n"/>
+      <c r="C57" s="32" t="n"/>
+      <c r="D57" s="32" t="n"/>
+      <c r="E57" s="32" t="n"/>
+      <c r="F57" s="32" t="n"/>
+    </row>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
@@ -3706,7 +3214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3802,22 +3310,22 @@
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="36" t="inlineStr">
         <is>
-          <t>Cardiologie USC</t>
+          <t>Urgences Adultes</t>
         </is>
       </c>
       <c r="B4" s="36" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="C4" s="36" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
+          <t>REA/URGENCES</t>
         </is>
       </c>
       <c r="D4" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E4" s="36" t="n">
@@ -3841,14 +3349,10 @@
       </c>
       <c r="J4" s="36" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K4" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K4" s="36" t="inlineStr"/>
       <c r="L4" s="36" t="n">
         <v>1</v>
       </c>
@@ -3856,29 +3360,29 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="36" t="inlineStr">
         <is>
-          <t>Cardiologie 1</t>
+          <t>Uhcd</t>
         </is>
       </c>
       <c r="B5" s="36" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
+          <t>REA/URGENCES</t>
         </is>
       </c>
       <c r="D5" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E5" s="36" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F5" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="36" t="n">
         <v>0</v>
@@ -3895,14 +3399,10 @@
       </c>
       <c r="J5" s="36" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K5" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K5" s="36" t="inlineStr"/>
       <c r="L5" s="36" t="n">
         <v>2</v>
       </c>
@@ -3910,32 +3410,32 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="36" t="inlineStr">
         <is>
-          <t>Cardiologie 2</t>
+          <t>Smur</t>
         </is>
       </c>
       <c r="B6" s="36" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="C6" s="36" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
+          <t>REA/URGENCES</t>
         </is>
       </c>
       <c r="D6" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E6" s="36" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F6" s="36" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="36" t="inlineStr">
         <is>
@@ -3949,14 +3449,10 @@
       </c>
       <c r="J6" s="36" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K6" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K6" s="36" t="inlineStr"/>
       <c r="L6" s="36" t="n">
         <v>3</v>
       </c>
@@ -3964,26 +3460,26 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="36" t="inlineStr">
         <is>
-          <t>Dermatologie</t>
+          <t>Urgences Pediatriques</t>
         </is>
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="C7" s="36" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
+          <t>REA/URGENCES</t>
         </is>
       </c>
       <c r="D7" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E7" s="36" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F7" s="36" t="n">
         <v>0</v>
@@ -4006,11 +3502,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K7" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K7" s="36" t="inlineStr"/>
       <c r="L7" s="36" t="n">
         <v>4</v>
       </c>
@@ -4018,26 +3510,26 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="36" t="inlineStr">
         <is>
-          <t>HDJ Médecine</t>
+          <t>Reanimation Adultes</t>
         </is>
       </c>
       <c r="B8" s="36" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="C8" s="36" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
+          <t>REA/URGENCES</t>
         </is>
       </c>
       <c r="D8" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E8" s="36" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8" s="36" t="n">
         <v>0</v>
@@ -4060,11 +3552,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K8" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K8" s="36" t="inlineStr"/>
       <c r="L8" s="36" t="n">
         <v>5</v>
       </c>
@@ -4072,26 +3560,26 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="36" t="inlineStr">
         <is>
-          <t>Hématologie</t>
+          <t>Soins Continus</t>
         </is>
       </c>
       <c r="B9" s="36" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="C9" s="36" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
+          <t>REA/URGENCES</t>
         </is>
       </c>
       <c r="D9" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E9" s="36" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F9" s="36" t="n">
         <v>0</v>
@@ -4114,11 +3602,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K9" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K9" s="36" t="inlineStr"/>
       <c r="L9" s="36" t="n">
         <v>6</v>
       </c>
@@ -4126,32 +3610,32 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="36" t="inlineStr">
         <is>
-          <t>Hépato-Gastroentérologie</t>
+          <t>Usic</t>
         </is>
       </c>
       <c r="B10" s="36" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="C10" s="36" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
+          <t>REA/URGENCES</t>
         </is>
       </c>
       <c r="D10" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E10" s="36" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F10" s="36" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="36" t="inlineStr">
         <is>
@@ -4168,11 +3652,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K10" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K10" s="36" t="inlineStr"/>
       <c r="L10" s="36" t="n">
         <v>7</v>
       </c>
@@ -4180,32 +3660,32 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="36" t="inlineStr">
         <is>
-          <t>Infectiologie HC</t>
+          <t>Bloc Operatoire Central</t>
         </is>
       </c>
       <c r="B11" s="36" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="C11" s="36" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
+          <t>CHIRURGIE</t>
         </is>
       </c>
       <c r="D11" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E11" s="36" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="36" t="inlineStr">
         <is>
@@ -4222,11 +3702,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K11" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K11" s="36" t="inlineStr"/>
       <c r="L11" s="36" t="n">
         <v>8</v>
       </c>
@@ -4234,32 +3710,32 @@
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="36" t="inlineStr">
         <is>
-          <t>Néphrologie</t>
+          <t>Chirurgie Viscerale</t>
         </is>
       </c>
       <c r="B12" s="36" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="C12" s="36" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
+          <t>CHIRURGIE</t>
         </is>
       </c>
       <c r="D12" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E12" s="36" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="36" t="inlineStr">
         <is>
@@ -4276,11 +3752,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K12" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K12" s="36" t="inlineStr"/>
       <c r="L12" s="36" t="n">
         <v>9</v>
       </c>
@@ -4288,32 +3760,32 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="36" t="inlineStr">
         <is>
-          <t>Neurologie</t>
+          <t>Chirurgie Orthopedique</t>
         </is>
       </c>
       <c r="B13" s="36" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="C13" s="36" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
+          <t>CHIRURGIE</t>
         </is>
       </c>
       <c r="D13" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E13" s="36" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F13" s="36" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="36" t="inlineStr">
         <is>
@@ -4327,14 +3799,10 @@
       </c>
       <c r="J13" s="36" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K13" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" s="36" t="inlineStr"/>
       <c r="L13" s="36" t="n">
         <v>10</v>
       </c>
@@ -4342,26 +3810,26 @@
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="36" t="inlineStr">
         <is>
-          <t>Neurologie Post-Aigu UNV</t>
+          <t>Chirurgie Ambulatoire</t>
         </is>
       </c>
       <c r="B14" s="36" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="C14" s="36" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
+          <t>CHIRURGIE</t>
         </is>
       </c>
       <c r="D14" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E14" s="36" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F14" s="36" t="n">
         <v>0</v>
@@ -4384,11 +3852,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K14" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K14" s="36" t="inlineStr"/>
       <c r="L14" s="36" t="n">
         <v>11</v>
       </c>
@@ -4396,12 +3860,12 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="36" t="inlineStr">
         <is>
-          <t>Neurologie SI UNV</t>
+          <t>Medecine Interne</t>
         </is>
       </c>
       <c r="B15" s="36" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="C15" s="36" t="inlineStr">
@@ -4411,11 +3875,11 @@
       </c>
       <c r="D15" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E15" s="36" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F15" s="36" t="n">
         <v>0</v>
@@ -4438,11 +3902,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K15" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K15" s="36" t="inlineStr"/>
       <c r="L15" s="36" t="n">
         <v>12</v>
       </c>
@@ -4450,12 +3910,12 @@
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="36" t="inlineStr">
         <is>
-          <t>Oncologie</t>
+          <t>Cardiologie</t>
         </is>
       </c>
       <c r="B16" s="36" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="C16" s="36" t="inlineStr">
@@ -4465,11 +3925,11 @@
       </c>
       <c r="D16" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E16" s="36" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F16" s="36" t="n">
         <v>0</v>
@@ -4492,11 +3952,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K16" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K16" s="36" t="inlineStr"/>
       <c r="L16" s="36" t="n">
         <v>13</v>
       </c>
@@ -4509,7 +3965,7 @@
       </c>
       <c r="B17" s="36" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="C17" s="36" t="inlineStr">
@@ -4519,11 +3975,11 @@
       </c>
       <c r="D17" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E17" s="36" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F17" s="36" t="n">
         <v>0</v>
@@ -4546,11 +4002,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K17" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K17" s="36" t="inlineStr"/>
       <c r="L17" s="36" t="n">
         <v>14</v>
       </c>
@@ -4558,12 +4010,12 @@
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="36" t="inlineStr">
         <is>
-          <t>Rhumatologie</t>
+          <t>Neurologie</t>
         </is>
       </c>
       <c r="B18" s="36" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="C18" s="36" t="inlineStr">
@@ -4573,11 +4025,11 @@
       </c>
       <c r="D18" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E18" s="36" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F18" s="36" t="n">
         <v>0</v>
@@ -4600,11 +4052,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K18" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K18" s="36" t="inlineStr"/>
       <c r="L18" s="36" t="n">
         <v>15</v>
       </c>
@@ -4612,12 +4060,12 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="36" t="inlineStr">
         <is>
-          <t>Gériatrie Aiguë</t>
+          <t>Gastro-Enterologie</t>
         </is>
       </c>
       <c r="B19" s="36" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="C19" s="36" t="inlineStr">
@@ -4627,11 +4075,11 @@
       </c>
       <c r="D19" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E19" s="36" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F19" s="36" t="n">
         <v>0</v>
@@ -4654,11 +4102,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K19" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K19" s="36" t="inlineStr"/>
       <c r="L19" s="36" t="n">
         <v>16</v>
       </c>
@@ -4666,12 +4110,12 @@
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="36" t="inlineStr">
         <is>
-          <t>UPUM</t>
+          <t>Infectiologie</t>
         </is>
       </c>
       <c r="B20" s="36" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="C20" s="36" t="inlineStr">
@@ -4681,11 +4125,11 @@
       </c>
       <c r="D20" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E20" s="36" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F20" s="36" t="n">
         <v>0</v>
@@ -4708,11 +4152,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K20" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K20" s="36" t="inlineStr"/>
       <c r="L20" s="36" t="n">
         <v>17</v>
       </c>
@@ -4720,12 +4160,12 @@
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="36" t="inlineStr">
         <is>
-          <t>Unité Hivernale</t>
+          <t>Nephrologie / Hemodialyse</t>
         </is>
       </c>
       <c r="B21" s="36" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="C21" s="36" t="inlineStr">
@@ -4735,11 +4175,11 @@
       </c>
       <c r="D21" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E21" s="36" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F21" s="36" t="n">
         <v>0</v>
@@ -4762,11 +4202,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K21" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K21" s="36" t="inlineStr"/>
       <c r="L21" s="36" t="n">
         <v>18</v>
       </c>
@@ -4774,26 +4210,26 @@
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="36" t="inlineStr">
         <is>
-          <t>Unité Hivernale 2</t>
+          <t>Maternite / Gynecologie</t>
         </is>
       </c>
       <c r="B22" s="36" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="C22" s="36" t="inlineStr">
         <is>
-          <t>MÉDECINE</t>
+          <t>FME</t>
         </is>
       </c>
       <c r="D22" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E22" s="36" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F22" s="36" t="n">
         <v>0</v>
@@ -4813,14 +4249,10 @@
       </c>
       <c r="J22" s="36" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K22" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K22" s="36" t="inlineStr"/>
       <c r="L22" s="36" t="n">
         <v>19</v>
       </c>
@@ -4828,26 +4260,26 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="36" t="inlineStr">
         <is>
-          <t>Chirurgie Cardiaque</t>
+          <t>Bloc Accouchement</t>
         </is>
       </c>
       <c r="B23" s="36" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="C23" s="36" t="inlineStr">
         <is>
-          <t>CHIRURGIE</t>
+          <t>FME</t>
         </is>
       </c>
       <c r="D23" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E23" s="36" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F23" s="36" t="n">
         <v>0</v>
@@ -4867,14 +4299,10 @@
       </c>
       <c r="J23" s="36" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K23" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K23" s="36" t="inlineStr"/>
       <c r="L23" s="36" t="n">
         <v>20</v>
       </c>
@@ -4882,32 +4310,32 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="36" t="inlineStr">
         <is>
-          <t>Chirurgie Digestive</t>
+          <t>Neonatologie</t>
         </is>
       </c>
       <c r="B24" s="36" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="C24" s="36" t="inlineStr">
         <is>
-          <t>CHIRURGIE</t>
+          <t>FME</t>
         </is>
       </c>
       <c r="D24" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E24" s="36" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F24" s="36" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="36" t="inlineStr">
         <is>
@@ -4921,14 +4349,10 @@
       </c>
       <c r="J24" s="36" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K24" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K24" s="36" t="inlineStr"/>
       <c r="L24" s="36" t="n">
         <v>21</v>
       </c>
@@ -4936,26 +4360,26 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="36" t="inlineStr">
         <is>
-          <t>Gynécologie Chir.</t>
+          <t>Pediatrie Generale</t>
         </is>
       </c>
       <c r="B25" s="36" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="C25" s="36" t="inlineStr">
         <is>
-          <t>CHIRURGIE</t>
+          <t>FME</t>
         </is>
       </c>
       <c r="D25" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E25" s="36" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F25" s="36" t="n">
         <v>0</v>
@@ -4965,24 +4389,20 @@
       </c>
       <c r="H25" s="36" t="inlineStr">
         <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I25" s="36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J25" s="36" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I25" s="36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J25" s="36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K25" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K25" s="36" t="inlineStr"/>
       <c r="L25" s="36" t="n">
         <v>22</v>
       </c>
@@ -4990,26 +4410,26 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="36" t="inlineStr">
         <is>
-          <t>Neurochirurgie</t>
+          <t>Court Sejour Geriatrique</t>
         </is>
       </c>
       <c r="B26" s="36" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="C26" s="36" t="inlineStr">
         <is>
-          <t>CHIRURGIE</t>
+          <t>LONG SÉJOUR</t>
         </is>
       </c>
       <c r="D26" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E26" s="36" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F26" s="36" t="n">
         <v>0</v>
@@ -5032,11 +4452,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K26" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K26" s="36" t="inlineStr"/>
       <c r="L26" s="36" t="n">
         <v>23</v>
       </c>
@@ -5044,32 +4460,32 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="36" t="inlineStr">
         <is>
-          <t>Orthopédie Traumatologie</t>
+          <t>Ssr Geriatrique</t>
         </is>
       </c>
       <c r="B27" s="36" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="C27" s="36" t="inlineStr">
         <is>
-          <t>CHIRURGIE</t>
+          <t>LONG SÉJOUR</t>
         </is>
       </c>
       <c r="D27" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E27" s="36" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="F27" s="36" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="36" t="inlineStr">
         <is>
@@ -5086,11 +4502,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K27" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K27" s="36" t="inlineStr"/>
       <c r="L27" s="36" t="n">
         <v>24</v>
       </c>
@@ -5098,26 +4510,26 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="36" t="inlineStr">
         <is>
-          <t>ORL / Ophtalmo / CMF</t>
+          <t>Ehpad</t>
         </is>
       </c>
       <c r="B28" s="36" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="C28" s="36" t="inlineStr">
         <is>
-          <t>CHIRURGIE</t>
+          <t>LONG SÉJOUR</t>
         </is>
       </c>
       <c r="D28" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 2</t>
         </is>
       </c>
       <c r="E28" s="36" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F28" s="36" t="n">
         <v>0</v>
@@ -5140,11 +4552,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K28" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K28" s="36" t="inlineStr"/>
       <c r="L28" s="36" t="n">
         <v>25</v>
       </c>
@@ -5152,32 +4560,32 @@
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="36" t="inlineStr">
         <is>
-          <t>Uro / Thoracique / Vasc.</t>
+          <t>Radiologie / Scanner</t>
         </is>
       </c>
       <c r="B29" s="36" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="C29" s="36" t="inlineStr">
         <is>
-          <t>CHIRURGIE</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="D29" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E29" s="36" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F29" s="36" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="36" t="inlineStr">
         <is>
@@ -5194,11 +4602,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K29" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K29" s="36" t="inlineStr"/>
       <c r="L29" s="36" t="n">
         <v>26</v>
       </c>
@@ -5206,26 +4610,26 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="36" t="inlineStr">
         <is>
-          <t>Réanimation</t>
+          <t>Radiologie / Scanner</t>
         </is>
       </c>
       <c r="B30" s="36" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="C30" s="36" t="inlineStr">
         <is>
-          <t>REA/URGENCES</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="D30" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 2</t>
         </is>
       </c>
       <c r="E30" s="36" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F30" s="36" t="n">
         <v>0</v>
@@ -5248,38 +4652,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K30" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K30" s="36" t="inlineStr"/>
       <c r="L30" s="36" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="36" t="inlineStr">
         <is>
-          <t>SIPO</t>
+          <t>Irm</t>
         </is>
       </c>
       <c r="B31" s="36" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="C31" s="36" t="inlineStr">
         <is>
-          <t>REA/URGENCES</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="D31" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E31" s="36" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F31" s="36" t="n">
         <v>0</v>
@@ -5302,38 +4702,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K31" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K31" s="36" t="inlineStr"/>
       <c r="L31" s="36" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="36" t="inlineStr">
         <is>
-          <t>UHCD</t>
+          <t>Laboratoire Biochimie</t>
         </is>
       </c>
       <c r="B32" s="36" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="C32" s="36" t="inlineStr">
         <is>
-          <t>REA/URGENCES</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="D32" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E32" s="36" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F32" s="36" t="n">
         <v>0</v>
@@ -5356,38 +4752,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K32" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K32" s="36" t="inlineStr"/>
       <c r="L32" s="36" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="36" t="inlineStr">
         <is>
-          <t>USIP</t>
+          <t>Laboratoire Biochimie</t>
         </is>
       </c>
       <c r="B33" s="36" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="C33" s="36" t="inlineStr">
         <is>
-          <t>REA/URGENCES</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="D33" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 2</t>
         </is>
       </c>
       <c r="E33" s="36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F33" s="36" t="n">
         <v>0</v>
@@ -5410,44 +4802,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K33" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K33" s="36" t="inlineStr"/>
       <c r="L33" s="36" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="36" t="inlineStr">
         <is>
-          <t>USIC</t>
+          <t>Laboratoire Microbiologie</t>
         </is>
       </c>
       <c r="B34" s="36" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="C34" s="36" t="inlineStr">
         <is>
-          <t>REA/URGENCES</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="D34" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E34" s="36" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F34" s="36" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34" s="36" t="inlineStr">
         <is>
@@ -5464,38 +4852,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K34" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K34" s="36" t="inlineStr"/>
       <c r="L34" s="36" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="36" t="inlineStr">
         <is>
-          <t>Soins Palliatifs</t>
+          <t>Laboratoire Microbiologie</t>
         </is>
       </c>
       <c r="B35" s="36" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="C35" s="36" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="D35" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 2</t>
         </is>
       </c>
       <c r="E35" s="36" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F35" s="36" t="n">
         <v>0</v>
@@ -5518,38 +4902,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K35" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K35" s="36" t="inlineStr"/>
       <c r="L35" s="36" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="36" t="inlineStr">
         <is>
-          <t>Grands Enfants</t>
+          <t>Pharmacie</t>
         </is>
       </c>
       <c r="B36" s="36" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="C36" s="36" t="inlineStr">
         <is>
-          <t>FME</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="D36" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E36" s="36" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F36" s="36" t="n">
         <v>0</v>
@@ -5572,38 +4952,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K36" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K36" s="36" t="inlineStr"/>
       <c r="L36" s="36" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="36" t="inlineStr">
         <is>
-          <t>Néonatologie</t>
+          <t>Pharmacie</t>
         </is>
       </c>
       <c r="B37" s="36" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="C37" s="36" t="inlineStr">
         <is>
-          <t>FME</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="D37" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 2</t>
         </is>
       </c>
       <c r="E37" s="36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F37" s="36" t="n">
         <v>0</v>
@@ -5626,34 +5002,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K37" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K37" s="36" t="inlineStr"/>
       <c r="L37" s="36" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="36" t="inlineStr">
         <is>
-          <t>SI Néonatologie</t>
-        </is>
-      </c>
-      <c r="B38" s="36" t="inlineStr"/>
+          <t>Sterilisation Centrale</t>
+        </is>
+      </c>
+      <c r="B38" s="36" t="inlineStr">
+        <is>
+          <t>8002</t>
+        </is>
+      </c>
       <c r="C38" s="36" t="inlineStr">
         <is>
-          <t>FME</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="D38" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E38" s="36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F38" s="36" t="n">
         <v>0</v>
@@ -5676,38 +5052,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K38" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K38" s="36" t="inlineStr"/>
       <c r="L38" s="36" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="36" t="inlineStr">
         <is>
-          <t>Nourrissons</t>
+          <t>Medecine Polyvalente</t>
         </is>
       </c>
       <c r="B39" s="36" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>9001</t>
         </is>
       </c>
       <c r="C39" s="36" t="inlineStr">
         <is>
-          <t>FME</t>
+          <t>MÉDECINE</t>
         </is>
       </c>
       <c r="D39" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 2</t>
         </is>
       </c>
       <c r="E39" s="36" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F39" s="36" t="n">
         <v>0</v>
@@ -5730,38 +5102,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K39" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX</t>
-        </is>
-      </c>
+      <c r="K39" s="36" t="inlineStr"/>
       <c r="L39" s="36" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="36" t="inlineStr">
         <is>
-          <t>Obstétrique</t>
+          <t>Bloc Operatoire Secondaire</t>
         </is>
       </c>
       <c r="B40" s="36" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="C40" s="36" t="inlineStr">
         <is>
-          <t>FME</t>
+          <t>CHIRURGIE</t>
         </is>
       </c>
       <c r="D40" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 2</t>
         </is>
       </c>
       <c r="E40" s="36" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F40" s="36" t="n">
         <v>0</v>
@@ -5771,7 +5139,7 @@
       </c>
       <c r="H40" s="36" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>O</t>
         </is>
       </c>
       <c r="I40" s="36" t="inlineStr">
@@ -5781,41 +5149,37 @@
       </c>
       <c r="J40" s="36" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K40" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" s="36" t="inlineStr"/>
       <c r="L40" s="36" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="36" t="inlineStr">
         <is>
-          <t>USIP Pédiatrie</t>
+          <t>Urgences Site Secondaire</t>
         </is>
       </c>
       <c r="B41" s="36" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>9003</t>
         </is>
       </c>
       <c r="C41" s="36" t="inlineStr">
         <is>
-          <t>FME</t>
+          <t>REA/URGENCES</t>
         </is>
       </c>
       <c r="D41" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 2</t>
         </is>
       </c>
       <c r="E41" s="36" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F41" s="36" t="n">
         <v>0</v>
@@ -5838,41 +5202,37 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K41" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K41" s="36" t="inlineStr"/>
       <c r="L41" s="36" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="36" t="inlineStr">
         <is>
-          <t>Psychiatrie adulte A</t>
+          <t>Direction Generale</t>
         </is>
       </c>
       <c r="B42" s="36" t="inlineStr">
         <is>
-          <t>8003</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="C42" s="36" t="inlineStr">
         <is>
-          <t>PSY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="D42" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E42" s="36" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F42" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G42" s="36" t="n">
         <v>0</v>
@@ -5892,38 +5252,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K42" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K42" s="36" t="inlineStr"/>
       <c r="L42" s="36" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="36" t="inlineStr">
         <is>
-          <t>UPUP</t>
+          <t>Dsi Informatique</t>
         </is>
       </c>
       <c r="B43" s="36" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="C43" s="36" t="inlineStr">
         <is>
-          <t>PSY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="D43" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E43" s="36" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F43" s="36" t="n">
         <v>0</v>
@@ -5946,38 +5302,34 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K43" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K43" s="36" t="inlineStr"/>
       <c r="L43" s="36" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="36" t="inlineStr">
         <is>
-          <t>UPUP Adolescents</t>
+          <t>Services Techniques</t>
         </is>
       </c>
       <c r="B44" s="36" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="C44" s="36" t="inlineStr">
         <is>
-          <t>PSY</t>
+          <t>SUPPORT</t>
         </is>
       </c>
       <c r="D44" s="36" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="E44" s="36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F44" s="36" t="n">
         <v>0</v>
@@ -6000,901 +5352,255 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K44" s="36" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
+      <c r="K44" s="36" t="inlineStr"/>
       <c r="L44" s="36" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="37" t="inlineStr">
-        <is>
-          <t>Addictologie</t>
-        </is>
-      </c>
-      <c r="B45" s="37" t="inlineStr">
-        <is>
-          <t>5020</t>
-        </is>
-      </c>
-      <c r="C45" s="37" t="inlineStr">
-        <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D45" s="37" t="inlineStr">
-        <is>
-          <t>Saint-Julien</t>
-        </is>
-      </c>
-      <c r="E45" s="37" t="n">
-        <v>12</v>
-      </c>
-      <c r="F45" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I45" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J45" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K45" s="37" t="inlineStr">
-        <is>
-          <t>XX XX XX</t>
-        </is>
-      </c>
-      <c r="L45" s="37" t="n">
-        <v>70</v>
-      </c>
+      <c r="A45" s="37" t="n"/>
+      <c r="B45" s="37" t="n"/>
+      <c r="C45" s="37" t="n"/>
+      <c r="D45" s="37" t="n"/>
+      <c r="E45" s="37" t="n"/>
+      <c r="F45" s="37" t="n"/>
+      <c r="G45" s="37" t="n"/>
+      <c r="H45" s="37" t="n"/>
+      <c r="I45" s="37" t="n"/>
+      <c r="J45" s="37" t="n"/>
+      <c r="K45" s="37" t="n"/>
+      <c r="L45" s="37" t="n"/>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="37" t="inlineStr">
-        <is>
-          <t>Cardiologie</t>
-        </is>
-      </c>
-      <c r="B46" s="37" t="inlineStr">
-        <is>
-          <t>5620</t>
-        </is>
-      </c>
-      <c r="C46" s="37" t="inlineStr">
-        <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D46" s="37" t="inlineStr">
-        <is>
-          <t>Saint-Julien</t>
-        </is>
-      </c>
-      <c r="E46" s="37" t="n">
-        <v>18</v>
-      </c>
-      <c r="F46" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I46" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J46" s="37" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K46" s="37" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
-      <c r="L46" s="37" t="n">
-        <v>71</v>
-      </c>
+      <c r="A46" s="37" t="n"/>
+      <c r="B46" s="37" t="n"/>
+      <c r="C46" s="37" t="n"/>
+      <c r="D46" s="37" t="n"/>
+      <c r="E46" s="37" t="n"/>
+      <c r="F46" s="37" t="n"/>
+      <c r="G46" s="37" t="n"/>
+      <c r="H46" s="37" t="n"/>
+      <c r="I46" s="37" t="n"/>
+      <c r="J46" s="37" t="n"/>
+      <c r="K46" s="37" t="n"/>
+      <c r="L46" s="37" t="n"/>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="37" t="inlineStr">
-        <is>
-          <t>Chirurgie</t>
-        </is>
-      </c>
-      <c r="B47" s="37" t="inlineStr">
-        <is>
-          <t>7320</t>
-        </is>
-      </c>
-      <c r="C47" s="37" t="inlineStr">
-        <is>
-          <t>CHIRURGIE</t>
-        </is>
-      </c>
-      <c r="D47" s="37" t="inlineStr">
-        <is>
-          <t>Saint-Julien</t>
-        </is>
-      </c>
-      <c r="E47" s="37" t="n">
-        <v>18</v>
-      </c>
-      <c r="F47" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I47" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J47" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K47" s="37" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
-      <c r="L47" s="37" t="n">
-        <v>72</v>
-      </c>
+      <c r="A47" s="37" t="n"/>
+      <c r="B47" s="37" t="n"/>
+      <c r="C47" s="37" t="n"/>
+      <c r="D47" s="37" t="n"/>
+      <c r="E47" s="37" t="n"/>
+      <c r="F47" s="37" t="n"/>
+      <c r="G47" s="37" t="n"/>
+      <c r="H47" s="37" t="n"/>
+      <c r="I47" s="37" t="n"/>
+      <c r="J47" s="37" t="n"/>
+      <c r="K47" s="37" t="n"/>
+      <c r="L47" s="37" t="n"/>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="37" t="inlineStr">
-        <is>
-          <t>Médecine Polyvalente</t>
-        </is>
-      </c>
-      <c r="B48" s="37" t="inlineStr">
-        <is>
-          <t>5430</t>
-        </is>
-      </c>
-      <c r="C48" s="37" t="inlineStr">
-        <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D48" s="37" t="inlineStr">
-        <is>
-          <t>Saint-Julien</t>
-        </is>
-      </c>
-      <c r="E48" s="37" t="n">
-        <v>24</v>
-      </c>
-      <c r="F48" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I48" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J48" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K48" s="37" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
-      <c r="L48" s="37" t="n">
-        <v>73</v>
-      </c>
+      <c r="A48" s="37" t="n"/>
+      <c r="B48" s="37" t="n"/>
+      <c r="C48" s="37" t="n"/>
+      <c r="D48" s="37" t="n"/>
+      <c r="E48" s="37" t="n"/>
+      <c r="F48" s="37" t="n"/>
+      <c r="G48" s="37" t="n"/>
+      <c r="H48" s="37" t="n"/>
+      <c r="I48" s="37" t="n"/>
+      <c r="J48" s="37" t="n"/>
+      <c r="K48" s="37" t="n"/>
+      <c r="L48" s="37" t="n"/>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="37" t="inlineStr">
-        <is>
-          <t>Neurologie UNV</t>
-        </is>
-      </c>
-      <c r="B49" s="37" t="inlineStr">
-        <is>
-          <t>5970</t>
-        </is>
-      </c>
-      <c r="C49" s="37" t="inlineStr">
-        <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D49" s="37" t="inlineStr">
-        <is>
-          <t>Saint-Julien</t>
-        </is>
-      </c>
-      <c r="E49" s="37" t="n">
-        <v>12</v>
-      </c>
-      <c r="F49" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I49" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J49" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K49" s="37" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
-      <c r="L49" s="37" t="n">
-        <v>74</v>
-      </c>
+      <c r="A49" s="37" t="n"/>
+      <c r="B49" s="37" t="n"/>
+      <c r="C49" s="37" t="n"/>
+      <c r="D49" s="37" t="n"/>
+      <c r="E49" s="37" t="n"/>
+      <c r="F49" s="37" t="n"/>
+      <c r="G49" s="37" t="n"/>
+      <c r="H49" s="37" t="n"/>
+      <c r="I49" s="37" t="n"/>
+      <c r="J49" s="37" t="n"/>
+      <c r="K49" s="37" t="n"/>
+      <c r="L49" s="37" t="n"/>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="37" t="inlineStr">
-        <is>
-          <t>Obstétrique</t>
-        </is>
-      </c>
-      <c r="B50" s="37" t="inlineStr">
-        <is>
-          <t>7740</t>
-        </is>
-      </c>
-      <c r="C50" s="37" t="inlineStr">
-        <is>
-          <t>FME</t>
-        </is>
-      </c>
-      <c r="D50" s="37" t="inlineStr">
-        <is>
-          <t>Saint-Julien</t>
-        </is>
-      </c>
-      <c r="E50" s="37" t="n">
-        <v>18</v>
-      </c>
-      <c r="F50" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="37" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I50" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J50" s="37" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K50" s="37" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
-      <c r="L50" s="37" t="n">
-        <v>75</v>
-      </c>
+      <c r="A50" s="37" t="n"/>
+      <c r="B50" s="37" t="n"/>
+      <c r="C50" s="37" t="n"/>
+      <c r="D50" s="37" t="n"/>
+      <c r="E50" s="37" t="n"/>
+      <c r="F50" s="37" t="n"/>
+      <c r="G50" s="37" t="n"/>
+      <c r="H50" s="37" t="n"/>
+      <c r="I50" s="37" t="n"/>
+      <c r="J50" s="37" t="n"/>
+      <c r="K50" s="37" t="n"/>
+      <c r="L50" s="37" t="n"/>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="37" t="inlineStr">
-        <is>
-          <t>Pneumologie</t>
-        </is>
-      </c>
-      <c r="B51" s="37" t="inlineStr">
-        <is>
-          <t>6140</t>
-        </is>
-      </c>
-      <c r="C51" s="37" t="inlineStr">
-        <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D51" s="37" t="inlineStr">
-        <is>
-          <t>Saint-Julien</t>
-        </is>
-      </c>
-      <c r="E51" s="37" t="n">
-        <v>10</v>
-      </c>
-      <c r="F51" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I51" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J51" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K51" s="37" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
-      <c r="L51" s="37" t="n">
-        <v>76</v>
-      </c>
+      <c r="A51" s="37" t="n"/>
+      <c r="B51" s="37" t="n"/>
+      <c r="C51" s="37" t="n"/>
+      <c r="D51" s="37" t="n"/>
+      <c r="E51" s="37" t="n"/>
+      <c r="F51" s="37" t="n"/>
+      <c r="G51" s="37" t="n"/>
+      <c r="H51" s="37" t="n"/>
+      <c r="I51" s="37" t="n"/>
+      <c r="J51" s="37" t="n"/>
+      <c r="K51" s="37" t="n"/>
+      <c r="L51" s="37" t="n"/>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="37" t="inlineStr">
-        <is>
-          <t>Soins Continus</t>
-        </is>
-      </c>
-      <c r="B52" s="37" t="inlineStr">
-        <is>
-          <t>7920</t>
-        </is>
-      </c>
-      <c r="C52" s="37" t="inlineStr">
-        <is>
-          <t>REA/URGENCES</t>
-        </is>
-      </c>
-      <c r="D52" s="37" t="inlineStr">
-        <is>
-          <t>Saint-Julien</t>
-        </is>
-      </c>
-      <c r="E52" s="37" t="n">
-        <v>8</v>
-      </c>
-      <c r="F52" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I52" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J52" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K52" s="37" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
-      <c r="L52" s="37" t="n">
-        <v>77</v>
-      </c>
+      <c r="A52" s="37" t="n"/>
+      <c r="B52" s="37" t="n"/>
+      <c r="C52" s="37" t="n"/>
+      <c r="D52" s="37" t="n"/>
+      <c r="E52" s="37" t="n"/>
+      <c r="F52" s="37" t="n"/>
+      <c r="G52" s="37" t="n"/>
+      <c r="H52" s="37" t="n"/>
+      <c r="I52" s="37" t="n"/>
+      <c r="J52" s="37" t="n"/>
+      <c r="K52" s="37" t="n"/>
+      <c r="L52" s="37" t="n"/>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="37" t="inlineStr">
-        <is>
-          <t>Gériatrie Aiguë</t>
-        </is>
-      </c>
-      <c r="B53" s="37" t="inlineStr">
-        <is>
-          <t>5550</t>
-        </is>
-      </c>
-      <c r="C53" s="37" t="inlineStr">
-        <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D53" s="37" t="inlineStr">
-        <is>
-          <t>Saint-Julien</t>
-        </is>
-      </c>
-      <c r="E53" s="37" t="n">
-        <v>10</v>
-      </c>
-      <c r="F53" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I53" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J53" s="37" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K53" s="37" t="inlineStr">
-        <is>
-          <t>XX XX XX / XX XX XX</t>
-        </is>
-      </c>
-      <c r="L53" s="37" t="n">
-        <v>78</v>
-      </c>
+      <c r="A53" s="37" t="n"/>
+      <c r="B53" s="37" t="n"/>
+      <c r="C53" s="37" t="n"/>
+      <c r="D53" s="37" t="n"/>
+      <c r="E53" s="37" t="n"/>
+      <c r="F53" s="37" t="n"/>
+      <c r="G53" s="37" t="n"/>
+      <c r="H53" s="37" t="n"/>
+      <c r="I53" s="37" t="n"/>
+      <c r="J53" s="37" t="n"/>
+      <c r="K53" s="37" t="n"/>
+      <c r="L53" s="37" t="n"/>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="38" t="inlineStr">
-        <is>
-          <t>Cardio-Gériatrie</t>
-        </is>
-      </c>
-      <c r="B54" s="38" t="inlineStr"/>
-      <c r="C54" s="38" t="inlineStr">
-        <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D54" s="38" t="inlineStr">
-        <is>
-          <t>Rumilly</t>
-        </is>
-      </c>
-      <c r="E54" s="38" t="n">
-        <v>10</v>
-      </c>
-      <c r="F54" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I54" s="38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J54" s="38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K54" s="38" t="inlineStr">
-        <is>
-          <t>04 50 00 00 00</t>
-        </is>
-      </c>
-      <c r="L54" s="38" t="n">
-        <v>80</v>
-      </c>
+      <c r="A54" s="38" t="n"/>
+      <c r="B54" s="38" t="n"/>
+      <c r="C54" s="38" t="n"/>
+      <c r="D54" s="38" t="n"/>
+      <c r="E54" s="38" t="n"/>
+      <c r="F54" s="38" t="n"/>
+      <c r="G54" s="38" t="n"/>
+      <c r="H54" s="38" t="n"/>
+      <c r="I54" s="38" t="n"/>
+      <c r="J54" s="38" t="n"/>
+      <c r="K54" s="38" t="n"/>
+      <c r="L54" s="38" t="n"/>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="38" t="inlineStr">
-        <is>
-          <t>Médecine</t>
-        </is>
-      </c>
-      <c r="B55" s="38" t="inlineStr"/>
-      <c r="C55" s="38" t="inlineStr">
-        <is>
-          <t>MÉDECINE</t>
-        </is>
-      </c>
-      <c r="D55" s="38" t="inlineStr">
-        <is>
-          <t>Rumilly</t>
-        </is>
-      </c>
-      <c r="E55" s="38" t="n">
-        <v>15</v>
-      </c>
-      <c r="F55" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I55" s="38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J55" s="38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K55" s="38" t="inlineStr">
-        <is>
-          <t>04 50 00 00 00</t>
-        </is>
-      </c>
-      <c r="L55" s="38" t="n">
-        <v>81</v>
-      </c>
+      <c r="A55" s="38" t="n"/>
+      <c r="B55" s="38" t="n"/>
+      <c r="C55" s="38" t="n"/>
+      <c r="D55" s="38" t="n"/>
+      <c r="E55" s="38" t="n"/>
+      <c r="F55" s="38" t="n"/>
+      <c r="G55" s="38" t="n"/>
+      <c r="H55" s="38" t="n"/>
+      <c r="I55" s="38" t="n"/>
+      <c r="J55" s="38" t="n"/>
+      <c r="K55" s="38" t="n"/>
+      <c r="L55" s="38" t="n"/>
     </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="39" t="inlineStr">
-        <is>
-          <t>USLD</t>
-        </is>
-      </c>
-      <c r="B56" s="39" t="inlineStr"/>
-      <c r="C56" s="39" t="inlineStr">
-        <is>
-          <t>LONG SÉJOUR</t>
-        </is>
-      </c>
-      <c r="D56" s="39" t="inlineStr">
-        <is>
-          <t>USLD/EHPAD</t>
-        </is>
-      </c>
-      <c r="E56" s="39" t="n">
-        <v>30</v>
-      </c>
-      <c r="F56" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I56" s="39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J56" s="39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K56" s="39" t="inlineStr">
-        <is>
-          <t>XX XX XX</t>
-        </is>
-      </c>
-      <c r="L56" s="39" t="n">
-        <v>90</v>
-      </c>
+      <c r="A56" s="39" t="n"/>
+      <c r="B56" s="39" t="n"/>
+      <c r="C56" s="39" t="n"/>
+      <c r="D56" s="39" t="n"/>
+      <c r="E56" s="39" t="n"/>
+      <c r="F56" s="39" t="n"/>
+      <c r="G56" s="39" t="n"/>
+      <c r="H56" s="39" t="n"/>
+      <c r="I56" s="39" t="n"/>
+      <c r="J56" s="39" t="n"/>
+      <c r="K56" s="39" t="n"/>
+      <c r="L56" s="39" t="n"/>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="39" t="inlineStr">
-        <is>
-          <t>UHR</t>
-        </is>
-      </c>
-      <c r="B57" s="39" t="inlineStr"/>
-      <c r="C57" s="39" t="inlineStr">
-        <is>
-          <t>LONG SÉJOUR</t>
-        </is>
-      </c>
-      <c r="D57" s="39" t="inlineStr">
-        <is>
-          <t>USLD/EHPAD</t>
-        </is>
-      </c>
-      <c r="E57" s="39" t="n">
-        <v>12</v>
-      </c>
-      <c r="F57" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I57" s="39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J57" s="39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K57" s="39" t="inlineStr">
-        <is>
-          <t>XX XX XX</t>
-        </is>
-      </c>
-      <c r="L57" s="39" t="n">
-        <v>91</v>
-      </c>
+      <c r="A57" s="39" t="n"/>
+      <c r="B57" s="39" t="n"/>
+      <c r="C57" s="39" t="n"/>
+      <c r="D57" s="39" t="n"/>
+      <c r="E57" s="39" t="n"/>
+      <c r="F57" s="39" t="n"/>
+      <c r="G57" s="39" t="n"/>
+      <c r="H57" s="39" t="n"/>
+      <c r="I57" s="39" t="n"/>
+      <c r="J57" s="39" t="n"/>
+      <c r="K57" s="39" t="n"/>
+      <c r="L57" s="39" t="n"/>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="39" t="inlineStr">
-        <is>
-          <t>UCC</t>
-        </is>
-      </c>
-      <c r="B58" s="39" t="inlineStr"/>
-      <c r="C58" s="39" t="inlineStr">
-        <is>
-          <t>LONG SÉJOUR</t>
-        </is>
-      </c>
-      <c r="D58" s="39" t="inlineStr">
-        <is>
-          <t>USLD/EHPAD</t>
-        </is>
-      </c>
-      <c r="E58" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="F58" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I58" s="39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J58" s="39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K58" s="39" t="inlineStr">
-        <is>
-          <t>XX XX XX</t>
-        </is>
-      </c>
-      <c r="L58" s="39" t="n">
-        <v>92</v>
-      </c>
+      <c r="A58" s="39" t="n"/>
+      <c r="B58" s="39" t="n"/>
+      <c r="C58" s="39" t="n"/>
+      <c r="D58" s="39" t="n"/>
+      <c r="E58" s="39" t="n"/>
+      <c r="F58" s="39" t="n"/>
+      <c r="G58" s="39" t="n"/>
+      <c r="H58" s="39" t="n"/>
+      <c r="I58" s="39" t="n"/>
+      <c r="J58" s="39" t="n"/>
+      <c r="K58" s="39" t="n"/>
+      <c r="L58" s="39" t="n"/>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="39" t="inlineStr">
-        <is>
-          <t>SMR</t>
-        </is>
-      </c>
-      <c r="B59" s="39" t="inlineStr"/>
-      <c r="C59" s="39" t="inlineStr">
-        <is>
-          <t>LONG SÉJOUR</t>
-        </is>
-      </c>
-      <c r="D59" s="39" t="inlineStr">
-        <is>
-          <t>USLD/EHPAD</t>
-        </is>
-      </c>
-      <c r="E59" s="39" t="n">
-        <v>28</v>
-      </c>
-      <c r="F59" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I59" s="39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J59" s="39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K59" s="39" t="inlineStr">
-        <is>
-          <t>XX XX XX</t>
-        </is>
-      </c>
-      <c r="L59" s="39" t="n">
-        <v>93</v>
-      </c>
+      <c r="A59" s="39" t="n"/>
+      <c r="B59" s="39" t="n"/>
+      <c r="C59" s="39" t="n"/>
+      <c r="D59" s="39" t="n"/>
+      <c r="E59" s="39" t="n"/>
+      <c r="F59" s="39" t="n"/>
+      <c r="G59" s="39" t="n"/>
+      <c r="H59" s="39" t="n"/>
+      <c r="I59" s="39" t="n"/>
+      <c r="J59" s="39" t="n"/>
+      <c r="K59" s="39" t="n"/>
+      <c r="L59" s="39" t="n"/>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="39" t="inlineStr">
-        <is>
-          <t>EHPAD 1</t>
-        </is>
-      </c>
-      <c r="B60" s="39" t="inlineStr"/>
-      <c r="C60" s="39" t="inlineStr">
-        <is>
-          <t>EHPAD</t>
-        </is>
-      </c>
-      <c r="D60" s="39" t="inlineStr">
-        <is>
-          <t>USLD/EHPAD</t>
-        </is>
-      </c>
-      <c r="E60" s="39" t="n">
-        <v>36</v>
-      </c>
-      <c r="F60" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I60" s="39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J60" s="39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K60" s="39" t="inlineStr">
-        <is>
-          <t>XX XX XX</t>
-        </is>
-      </c>
-      <c r="L60" s="39" t="n">
-        <v>94</v>
-      </c>
+      <c r="A60" s="39" t="n"/>
+      <c r="B60" s="39" t="n"/>
+      <c r="C60" s="39" t="n"/>
+      <c r="D60" s="39" t="n"/>
+      <c r="E60" s="39" t="n"/>
+      <c r="F60" s="39" t="n"/>
+      <c r="G60" s="39" t="n"/>
+      <c r="H60" s="39" t="n"/>
+      <c r="I60" s="39" t="n"/>
+      <c r="J60" s="39" t="n"/>
+      <c r="K60" s="39" t="n"/>
+      <c r="L60" s="39" t="n"/>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="39" t="inlineStr">
-        <is>
-          <t>EHPAD 2</t>
-        </is>
-      </c>
-      <c r="B61" s="39" t="inlineStr"/>
-      <c r="C61" s="39" t="inlineStr">
-        <is>
-          <t>EHPAD</t>
-        </is>
-      </c>
-      <c r="D61" s="39" t="inlineStr">
-        <is>
-          <t>USLD/EHPAD</t>
-        </is>
-      </c>
-      <c r="E61" s="39" t="n">
-        <v>88</v>
-      </c>
-      <c r="F61" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="I61" s="39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J61" s="39" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K61" s="39" t="inlineStr">
-        <is>
-          <t>XX XX XX</t>
-        </is>
-      </c>
-      <c r="L61" s="39" t="n">
-        <v>95</v>
-      </c>
-    </row>
+      <c r="A61" s="39" t="n"/>
+      <c r="B61" s="39" t="n"/>
+      <c r="C61" s="39" t="n"/>
+      <c r="D61" s="39" t="n"/>
+      <c r="E61" s="39" t="n"/>
+      <c r="F61" s="39" t="n"/>
+      <c r="G61" s="39" t="n"/>
+      <c r="H61" s="39" t="n"/>
+      <c r="I61" s="39" t="n"/>
+      <c r="J61" s="39" t="n"/>
+      <c r="K61" s="39" t="n"/>
+      <c r="L61" s="39" t="n"/>
+    </row>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
